--- a/data/trans_camb/P1416-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1416-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>2,78</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 5,77</t>
+          <t>-2,18; 5,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,72</t>
+          <t>-3,28; 4,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 15,88</t>
+          <t>0,7; 10,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 11,15</t>
+          <t>1,07; 11,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 8,89</t>
+          <t>-0,01; 9,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,77</t>
+          <t>-2,43; 4,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,84</t>
+          <t>0,77; 6,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,49</t>
+          <t>-0,42; 5,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 8,79</t>
+          <t>-0,29; 5,73</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143,98%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,5%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 166,34</t>
+          <t>-30,58; 145,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,68; 136,0</t>
+          <t>-47,02; 131,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,3; 380,04</t>
+          <t>2,66; 256,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 334,98</t>
+          <t>11,83; 334,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 286,41</t>
+          <t>-3,19; 283,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,72; 86,1</t>
+          <t>-37,69; 142,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 172,76</t>
+          <t>10,52; 163,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 137,14</t>
+          <t>-9,14; 132,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 205,69</t>
+          <t>-4,24; 147,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>5,65</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>3,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,06</t>
+          <t>-3,98; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,26</t>
+          <t>-5,83; -0,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,04</t>
+          <t>1,61; 10,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,1</t>
+          <t>-6,73; 0,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,18</t>
+          <t>-6,51; 0,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 6,09</t>
+          <t>-1,66; 5,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,41</t>
+          <t>-4,31; 0,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; -0,8</t>
+          <t>-5,17; -0,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,24</t>
+          <t>0,81; 6,55</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 65,02</t>
+          <t>-49,73; 55,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,02; -3,07</t>
+          <t>-69,52; 4,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 233,92</t>
+          <t>15,22; 212,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,67; 1,71</t>
+          <t>-56,12; 3,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 4,19</t>
+          <t>-52,45; 8,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 71,39</t>
+          <t>-14,03; 66,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 6,7</t>
+          <t>-44,02; 6,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,85; -11,57</t>
+          <t>-52,65; -8,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,75; 98,75</t>
+          <t>7,58; 87,7</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>4,81</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,78</t>
+          <t>-3,65; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,18</t>
+          <t>-3,44; 3,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,27</t>
+          <t>0,89; 8,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 5,37</t>
+          <t>-3,45; 4,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 0,52</t>
+          <t>-6,63; 0,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 7,43</t>
+          <t>-0,89; 7,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,95</t>
+          <t>-2,35; 2,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,73</t>
+          <t>-3,64; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,76</t>
+          <t>1,22; 6,7</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109,4%</t>
+          <t>111,46%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 99,93</t>
+          <t>-62,05; 118,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,05; 115,26</t>
+          <t>-54,37; 113,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 331,03</t>
+          <t>5,51; 321,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 104,09</t>
+          <t>-37,68; 85,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 11,09</t>
+          <t>-70,43; 9,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 145,49</t>
+          <t>-11,43; 138,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 65,83</t>
+          <t>-32,86; 61,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,1; 18,1</t>
+          <t>-53,19; 22,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,39; 155,51</t>
+          <t>14,88; 146,91</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-3,78</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,14</t>
+          <t>-5,84</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,39</t>
+          <t>-4,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; -0,45</t>
+          <t>-7,81; -0,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,52</t>
+          <t>-7,26; 0,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 1,55</t>
+          <t>-7,53; 1,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 0,36</t>
+          <t>-7,92; 0,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,84</t>
+          <t>-7,04; 2,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,91; -3,12</t>
+          <t>-10,11; -2,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -1,3</t>
+          <t>-6,86; -1,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 0,12</t>
+          <t>-5,92; -0,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -2,54</t>
+          <t>-7,72; -2,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-39,8%</t>
+          <t>-44,05%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-62,31%</t>
+          <t>-51,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-53,67%</t>
+          <t>-47,91%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,73; -2,39</t>
+          <t>-70,79; -3,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 11,21</t>
+          <t>-67,97; 16,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,17; 30,17</t>
+          <t>-72,44; 24,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,33; 7,46</t>
+          <t>-59,02; 4,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 21,0</t>
+          <t>-49,53; 27,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,76; -34,73</t>
+          <t>-71,3; -24,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-58,38; -14,83</t>
+          <t>-58,57; -14,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 2,93</t>
+          <t>-50,47; -0,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -29,81</t>
+          <t>-65,6; -21,01</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 3,93</t>
+          <t>-6,81; 4,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 1,97</t>
+          <t>-8,4; 1,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 7,61</t>
+          <t>-4,69; 6,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 5,45</t>
+          <t>-7,0; 6,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 1,36</t>
+          <t>-10,42; 1,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 4,53</t>
+          <t>-7,45; 4,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,9</t>
+          <t>-5,29; 3,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 0,44</t>
+          <t>-7,89; 0,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 4,62</t>
+          <t>-4,46; 3,73</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,68%</t>
+          <t>-9,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>-0,75%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,64; 65,22</t>
+          <t>-58,98; 76,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,91; 40,48</t>
+          <t>-70,98; 33,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 137,22</t>
+          <t>-38,91; 110,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,01; 58,12</t>
+          <t>-43,51; 63,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,14; 18,96</t>
+          <t>-64,52; 20,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,56; 48,63</t>
+          <t>-44,57; 46,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,97; 34,6</t>
+          <t>-41,06; 38,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 6,81</t>
+          <t>-60,5; 4,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 54,83</t>
+          <t>-32,51; 45,65</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,39</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,5</t>
+          <t>8,81</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>8,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 4,4</t>
+          <t>-4,01; 4,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 4,85</t>
+          <t>-2,93; 4,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,76; 13,53</t>
+          <t>3,77; 13,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 0,68</t>
+          <t>-7,8; 0,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 2,74</t>
+          <t>-6,57; 2,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,44; 13,81</t>
+          <t>3,28; 14,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,79</t>
+          <t>-4,64; 1,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,47</t>
+          <t>-3,91; 2,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,28; 12,1</t>
+          <t>4,66; 11,78</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>151,86%</t>
+          <t>151,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>114,2%</t>
+          <t>116,63%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 131,55</t>
+          <t>-52,47; 132,6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 138,39</t>
+          <t>-42,8; 129,19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44,62; 402,4</t>
+          <t>48,33; 379,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 12,44</t>
+          <t>-69,24; 21,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 43,61</t>
+          <t>-58,06; 44,35</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,14; 204,25</t>
+          <t>24,42; 211,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 33,0</t>
+          <t>-52,02; 26,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 44,58</t>
+          <t>-42,95; 40,39</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43,37; 207,01</t>
+          <t>49,0; 206,81</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7,21</t>
+          <t>7,96</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,38</t>
+          <t>10,93</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>9,52</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,42</t>
+          <t>-3,17; 1,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,81</t>
+          <t>-3,57; 0,91</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,57</t>
+          <t>5,28; 11,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,04</t>
+          <t>-3,46; 1,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 4,27</t>
+          <t>-1,4; 4,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 11,47</t>
+          <t>7,6; 14,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,97</t>
+          <t>-2,57; 0,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,79</t>
+          <t>-1,67; 1,71</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,8</t>
+          <t>7,48; 11,89</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>169,2%</t>
+          <t>186,93%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>170,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>128,39%</t>
+          <t>177,8%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,55; 49,17</t>
+          <t>-56,51; 45,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 32,41</t>
+          <t>-64,33; 37,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>65,74; 336,76</t>
+          <t>91,66; 377,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 44,37</t>
+          <t>-44,71; 35,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 79,42</t>
+          <t>-18,61; 83,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 200,08</t>
+          <t>94,18; 288,61</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 21,52</t>
+          <t>-40,41; 19,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 41,25</t>
+          <t>-28,25; 39,86</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>38,51; 203,79</t>
+          <t>115,65; 269,92</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,22</t>
+          <t>-2,52</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,55</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,34</t>
+          <t>-2,01</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -1,77</t>
+          <t>-6,74; -1,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,21</t>
+          <t>-5,8; 0,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -0,93</t>
+          <t>-5,52; 0,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,14; -3,18</t>
+          <t>-9,05; -3,1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 0,11</t>
+          <t>-6,61; 0,16</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1,36</t>
+          <t>-4,51; 1,49</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -3,12</t>
+          <t>-7,06; -2,84</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -0,97</t>
+          <t>-5,09; -1,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -1,16</t>
+          <t>-4,34; -0,09</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-45,76%</t>
+          <t>-27,38%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-12,33%</t>
+          <t>-11,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-30,5%</t>
+          <t>-18,37%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-63,94; -20,2</t>
+          <t>-63,55; -16,2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-52,62; -1,27</t>
+          <t>-51,73; 4,44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-77,47; -11,19</t>
+          <t>-51,63; 4,19</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-64,76; -29,28</t>
+          <t>-63,17; -28,51</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 2,87</t>
+          <t>-47,11; 1,32</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 13,16</t>
+          <t>-30,97; 14,61</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-59,04; -31,68</t>
+          <t>-59,25; -29,85</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,7; -9,72</t>
+          <t>-42,18; -10,96</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-59,6; -11,48</t>
+          <t>-35,29; -1,01</t>
         </is>
       </c>
     </row>
@@ -2362,37 +2362,37 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>3,03</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>-2,27</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>-1,65</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-1,92</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
           <t>2,72</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,65</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,43</t>
+          <t>-2,8; -0,36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,56</t>
+          <t>-2,94; -0,72</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,45</t>
+          <t>1,52; 4,48</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,89</t>
+          <t>-3,55; -0,92</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -0,4</t>
+          <t>-3,1; -0,32</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,72</t>
+          <t>1,01; 3,85</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,93</t>
+          <t>-2,83; -1,07</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,66</t>
+          <t>-2,6; -0,81</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,21</t>
+          <t>1,71; 3,69</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-38,12; -7,04</t>
+          <t>-38,15; -5,65</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -8,06</t>
+          <t>-39,98; -11,15</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7,23; 72,31</t>
+          <t>21,28; 72,59</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -9,92</t>
+          <t>-34,62; -10,31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-29,87; -4,33</t>
+          <t>-29,98; -4,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 30,11</t>
+          <t>9,45; 42,68</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -12,32</t>
+          <t>-32,55; -13,24</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-29,92; -8,68</t>
+          <t>-30,16; -10,05</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6,71; 41,67</t>
+          <t>19,52; 47,47</t>
         </is>
       </c>
     </row>
